--- a/frontend/public/ejemplos/ppe_propiedad_planta/RQ-002_adiciones.xlsx
+++ b/frontend/public/ejemplos/ppe_propiedad_planta/RQ-002_adiciones.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Léame" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Instrucciones" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,16 +26,60 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F6B4C"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="006B7280"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F6B4C"/>
+    </font>
+    <font>
+      <color rgb="006B7280"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F6B4C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006B7280"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F1EC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +87,46 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D1D5DB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,208 +494,218 @@
   </sheetPr>
   <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>N° de documento</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Código del activo</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Fecha del desembolso</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Tipo (capitalizable / reparación / mantenimiento)</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Importe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Activo apto (Sí/No)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Intereses capitalizados registrados</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>AD-01</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>OBRA-01</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>01/03/2025</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Avance de obra 1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Capitalizable</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>150000</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>AD-02</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>OBRA-01</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>01/09/2025</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>Avance de obra 2</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Capitalizable</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>45000</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>AD-03</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>OBRA-01</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>15/10/2025</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Cubierta provisional</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Reparación</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>5000</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>AD-04</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>MOB-01</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>01/04/2025</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Escritorios y sillas</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Capitalizable</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>12000</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -630,36 +718,169 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>AuditConsulting Auditores Cía. Ltda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Detalle de adiciones del año por documento</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Una fila por documento: N° de documento, código del activo, fecha, descripción, tipo, importe, activo apto (Sí/No) e intereses capitalizados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Formato de ejemplo con datos ficticios que muestra la estructura esperada. La hoja «Datos» trae los rótulos que la prueba reconoce automáticamente; reemplace las filas por las de su empresa. Si su archivo usa otros nombres de columna, puede cargarlo igual: al procesar podrá mapear a mano dónde está cada dato.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>EJEMPLO · datos ficticios</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Detalle de adiciones del año por documento</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Una fila por documento: N° de documento, código del activo, fecha, descripción, tipo, importe, activo apto (Sí/No) e intereses capitalizados.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Formato de ejemplo con datos ficticios que muestra la estructura esperada. La hoja «Datos» trae los rótulos que la prueba reconoce automáticamente; reemplace las filas por las de su empresa sin cambiar los encabezados.</t>
-        </is>
-      </c>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Columna</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Obligatoria</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Qué va aquí (ejemplo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>N° de documento</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Código del activo</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Fecha del desembolso</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Tipo (capitalizable / reparación / mantenimiento)</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Importe</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Activo apto (Sí/No)</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Intereses capitalizados registrados</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
